--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/IDAHO_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/IDAHO_2012.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C44">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C88">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C427">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C600">
